--- a/outputs/47827.xlsx
+++ b/outputs/47827.xlsx
@@ -207,60 +207,64 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -519,379 +523,379 @@
   <dimension ref="A1:L34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="6.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="10.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="6.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4" t="s">
+      <c r="F1" s="4"/>
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="n">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="7" t="n">
+      <c r="C2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="8" t="n">
         <v>410</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="8" t="s">
+      <c r="F2" s="7"/>
+      <c r="G2" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="8" t="s">
+      <c r="B3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6" t="n">
+      <c r="B4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="7"/>
+      <c r="G4" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="6" t="n">
+      <c r="B5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6" t="n">
+      <c r="B6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="7"/>
+      <c r="G6" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6" t="n">
+      <c r="B7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="7"/>
+      <c r="G7" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6" t="n">
+      <c r="B8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="9" t="n">
+      <c r="D8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="8" t="s">
+      <c r="F8" s="7"/>
+      <c r="G8" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="n">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="n">
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="7"/>
+      <c r="G9" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6" t="n">
+      <c r="B10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>105</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="8" t="s">
+      <c r="F10" s="7"/>
+      <c r="G10" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="6" t="n">
+      <c r="B11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9" t="n">
+      <c r="D11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="7"/>
+      <c r="G11" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6" t="n">
+      <c r="C12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="11" t="n">
         <v>303</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="8" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="7" t="n">
+      <c r="D13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="n">
         <v>321</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="8" t="s">
+      <c r="F13" s="7"/>
+      <c r="G13" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="10" t="n">
+      <c r="D14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11" t="n">
         <v>330</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="8" t="s">
+      <c r="F14" s="7"/>
+      <c r="G14" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="9" t="n">
+      <c r="C15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10" t="n">
         <v>501</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="8" t="s">
+      <c r="F15" s="7"/>
+      <c r="G15" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="9" t="n">
+      <c r="C16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="n">
         <v>510</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="8" t="s">
+      <c r="F16" s="7"/>
+      <c r="G16" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11"/>
-      <c r="E17" s="1"/>
+      <c r="A17" s="12"/>
+      <c r="E17" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J29" s="12"/>
-      <c r="L29" s="12"/>
+      <c r="J29" s="13"/>
+      <c r="L29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J30" s="12"/>
-      <c r="L30" s="12"/>
+      <c r="J30" s="13"/>
+      <c r="L30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J31" s="12"/>
-      <c r="L31" s="12"/>
+      <c r="J31" s="13"/>
+      <c r="L31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J32" s="12"/>
-      <c r="L32" s="12"/>
+      <c r="J32" s="13"/>
+      <c r="L32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J33" s="12"/>
-      <c r="L33" s="12"/>
+      <c r="J33" s="13"/>
+      <c r="L33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J34" s="12"/>
-      <c r="L34" s="12"/>
+      <c r="J34" s="13"/>
+      <c r="L34" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -913,410 +917,410 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1" t="n">
+      <c r="A2" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="n">
+      <c r="A3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="B4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="B5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="B7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="B8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="B9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1" t="n">
+      <c r="A10" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="B11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="2" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="n">
+      <c r="B12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="0" t="n">
+      <c r="B13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="2" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="B14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="2" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="0" t="n">
+      <c r="B15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="0" t="n">
+      <c r="B16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="2" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="0" t="n">
+      <c r="B17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="2" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="0" t="n">
+      <c r="B18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="2" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="12" t="n">
         <v>888</v>
       </c>
-      <c r="B21" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="C21" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D21" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" s="1" t="n">
+      <c r="B21" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="n">
         <v>888</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="12" t="n">
         <v>889</v>
       </c>
-      <c r="B22" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="C22" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" s="0" t="n">
+      <c r="B22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="2" t="n">
         <v>889</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="12" t="n">
         <v>899</v>
       </c>
-      <c r="B23" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="C23" s="0" t="n">
+      <c r="B23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E23" s="2" t="n">
         <v>899</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="12" t="n">
         <v>999</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D24" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E24" s="2" t="n">
         <v>999</v>
       </c>
     </row>
